--- a/nba_player_stats.xlsx
+++ b/nba_player_stats.xlsx
@@ -545,28 +545,28 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="E2">
-        <v>5.68</v>
+        <v>26.86</v>
       </c>
       <c r="F2">
-        <v>74.94</v>
+        <v>37.79</v>
       </c>
       <c r="G2">
-        <v>93.51000000000001</v>
+        <v>84.36</v>
       </c>
       <c r="H2">
-        <v>87.01000000000001</v>
+        <v>61.18</v>
       </c>
       <c r="I2">
-        <v>25.62</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="J2">
-        <v>39.41</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -577,28 +577,28 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1">
-        <v>46081</v>
+        <v>46085</v>
       </c>
       <c r="E3">
-        <v>21.42</v>
+        <v>25.51</v>
       </c>
       <c r="F3">
-        <v>26.78</v>
+        <v>86.36</v>
       </c>
       <c r="G3">
-        <v>80.95999999999999</v>
+        <v>42.93</v>
       </c>
       <c r="H3">
-        <v>33.93</v>
+        <v>79.97</v>
       </c>
       <c r="I3">
-        <v>66.56</v>
+        <v>34.43</v>
       </c>
       <c r="J3">
-        <v>25.5</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -609,28 +609,28 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D4" s="1">
         <v>46085</v>
       </c>
       <c r="E4">
-        <v>15.79</v>
+        <v>4.66</v>
       </c>
       <c r="F4">
-        <v>31.22</v>
+        <v>74.16</v>
       </c>
       <c r="G4">
-        <v>27.36</v>
+        <v>49.7</v>
       </c>
       <c r="H4">
-        <v>65.33</v>
+        <v>91.34</v>
       </c>
       <c r="I4">
-        <v>76.5</v>
+        <v>32.46</v>
       </c>
       <c r="J4">
-        <v>43.66</v>
+        <v>67.81</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -641,28 +641,28 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E5">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="F5">
-        <v>56.46</v>
+        <v>47.65</v>
       </c>
       <c r="G5">
-        <v>88.73999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H5">
-        <v>66.59</v>
+        <v>62.48</v>
       </c>
       <c r="I5">
-        <v>27.81</v>
+        <v>40.97</v>
       </c>
       <c r="J5">
-        <v>61.34</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -673,28 +673,28 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="E6">
-        <v>28.38</v>
+        <v>16.52</v>
       </c>
       <c r="F6">
-        <v>34.46</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G6">
-        <v>30.64</v>
+        <v>88.44</v>
       </c>
       <c r="H6">
-        <v>49.97</v>
+        <v>44.82</v>
       </c>
       <c r="I6">
-        <v>40.82</v>
+        <v>68.87</v>
       </c>
       <c r="J6">
-        <v>77.02</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -705,28 +705,28 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="E7">
-        <v>14.88</v>
+        <v>11.37</v>
       </c>
       <c r="F7">
-        <v>73.37</v>
+        <v>52.56</v>
       </c>
       <c r="G7">
-        <v>86.05</v>
+        <v>66.28</v>
       </c>
       <c r="H7">
-        <v>31.82</v>
+        <v>59.48</v>
       </c>
       <c r="I7">
-        <v>91.34</v>
+        <v>33.71</v>
       </c>
       <c r="J7">
-        <v>29.43</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -737,28 +737,28 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1">
         <v>46085</v>
       </c>
       <c r="E8">
-        <v>2.37</v>
+        <v>12.85</v>
       </c>
       <c r="F8">
-        <v>89.45999999999999</v>
+        <v>53.9</v>
       </c>
       <c r="G8">
-        <v>46.01</v>
+        <v>42.94</v>
       </c>
       <c r="H8">
-        <v>46.4</v>
+        <v>33.39</v>
       </c>
       <c r="I8">
-        <v>81.8</v>
+        <v>26.41</v>
       </c>
       <c r="J8">
-        <v>90.08</v>
+        <v>87.55</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -769,28 +769,28 @@
         <v>28</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="E9">
-        <v>1.76</v>
+        <v>10.47</v>
       </c>
       <c r="F9">
-        <v>75.05</v>
+        <v>35.58</v>
       </c>
       <c r="G9">
-        <v>46.84</v>
+        <v>79.38</v>
       </c>
       <c r="H9">
-        <v>25.27</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="I9">
-        <v>91.66</v>
+        <v>37.74</v>
       </c>
       <c r="J9">
-        <v>54.75</v>
+        <v>86.23999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -801,28 +801,28 @@
         <v>29</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="E10">
-        <v>5.56</v>
+        <v>15.5</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>80.95</v>
       </c>
       <c r="G10">
-        <v>25.67</v>
+        <v>80.97</v>
       </c>
       <c r="H10">
-        <v>71.04000000000001</v>
+        <v>35.27</v>
       </c>
       <c r="I10">
-        <v>46.17</v>
+        <v>28.31</v>
       </c>
       <c r="J10">
-        <v>37.85</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -833,28 +833,28 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="E11">
-        <v>1.89</v>
+        <v>17.7</v>
       </c>
       <c r="F11">
-        <v>55.91</v>
+        <v>30.05</v>
       </c>
       <c r="G11">
-        <v>46.25</v>
+        <v>69.13</v>
       </c>
       <c r="H11">
-        <v>62.37</v>
+        <v>69.84</v>
       </c>
       <c r="I11">
-        <v>79.56999999999999</v>
+        <v>53.89</v>
       </c>
       <c r="J11">
-        <v>86.84</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -865,28 +865,28 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1">
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="E12">
-        <v>11.61</v>
+        <v>21.94</v>
       </c>
       <c r="F12">
-        <v>58.5</v>
+        <v>27.16</v>
       </c>
       <c r="G12">
-        <v>50.03</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H12">
-        <v>26.01</v>
+        <v>38.15</v>
       </c>
       <c r="I12">
-        <v>94.62</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="J12">
-        <v>25.39</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -897,28 +897,28 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1">
-        <v>46079</v>
+        <v>46082</v>
       </c>
       <c r="E13">
-        <v>25.74</v>
+        <v>12.56</v>
       </c>
       <c r="F13">
-        <v>84.76000000000001</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="G13">
-        <v>75.52</v>
+        <v>35.79</v>
       </c>
       <c r="H13">
-        <v>64.02</v>
+        <v>59.21</v>
       </c>
       <c r="I13">
-        <v>35.27</v>
+        <v>79.34</v>
       </c>
       <c r="J13">
-        <v>89.11</v>
+        <v>54.01</v>
       </c>
     </row>
   </sheetData>
@@ -971,28 +971,28 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E2">
-        <v>21.18</v>
+        <v>18.26</v>
       </c>
       <c r="F2">
-        <v>77.63</v>
+        <v>46.77</v>
       </c>
       <c r="G2">
-        <v>70.27</v>
+        <v>35.92</v>
       </c>
       <c r="H2">
-        <v>33.84</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="I2">
-        <v>70.88</v>
+        <v>52.96</v>
       </c>
       <c r="J2">
-        <v>84.20999999999999</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1003,28 +1003,28 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="E3">
-        <v>25.3</v>
+        <v>16.21</v>
       </c>
       <c r="F3">
-        <v>51.35</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="G3">
-        <v>42.75</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="H3">
-        <v>68.59</v>
+        <v>88.19</v>
       </c>
       <c r="I3">
-        <v>76.12</v>
+        <v>94.81</v>
       </c>
       <c r="J3">
-        <v>28.08</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1035,28 +1035,28 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="D4" s="1">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="E4">
-        <v>26.13</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F4">
-        <v>27.13</v>
+        <v>49.76</v>
       </c>
       <c r="G4">
-        <v>68.01000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="H4">
-        <v>65.70999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="I4">
-        <v>57.22</v>
+        <v>64.67</v>
       </c>
       <c r="J4">
-        <v>49.23</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1067,28 +1067,28 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="E5">
-        <v>24.28</v>
+        <v>26.61</v>
       </c>
       <c r="F5">
-        <v>72.09</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="G5">
-        <v>94.08</v>
+        <v>41.72</v>
       </c>
       <c r="H5">
-        <v>65.89</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I5">
-        <v>66.81999999999999</v>
+        <v>32.96</v>
       </c>
       <c r="J5">
-        <v>42.26</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1099,28 +1099,28 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D6" s="1">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E6">
-        <v>15.08</v>
+        <v>9.49</v>
       </c>
       <c r="F6">
-        <v>52.96</v>
+        <v>47.69</v>
       </c>
       <c r="G6">
-        <v>51.43</v>
+        <v>30.68</v>
       </c>
       <c r="H6">
-        <v>78.44</v>
+        <v>91.53</v>
       </c>
       <c r="I6">
-        <v>29.52</v>
+        <v>82.16</v>
       </c>
       <c r="J6">
-        <v>37.1</v>
+        <v>93.97</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1131,28 +1131,28 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="E7">
-        <v>1.19</v>
+        <v>15.33</v>
       </c>
       <c r="F7">
-        <v>64.03</v>
+        <v>43.8</v>
       </c>
       <c r="G7">
-        <v>92.75</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="H7">
-        <v>44.35</v>
+        <v>39.45</v>
       </c>
       <c r="I7">
-        <v>64.73</v>
+        <v>49.99</v>
       </c>
       <c r="J7">
-        <v>60.83</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1163,28 +1163,28 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1">
-        <v>46080</v>
+        <v>46082</v>
       </c>
       <c r="E8">
-        <v>26.12</v>
+        <v>1.91</v>
       </c>
       <c r="F8">
-        <v>80.04000000000001</v>
+        <v>62.76</v>
       </c>
       <c r="G8">
-        <v>75.28</v>
+        <v>62.87</v>
       </c>
       <c r="H8">
-        <v>46.58</v>
+        <v>42.88</v>
       </c>
       <c r="I8">
-        <v>70.44</v>
+        <v>50.15</v>
       </c>
       <c r="J8">
-        <v>27.19</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1195,28 +1195,28 @@
         <v>28</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D9" s="1">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="E9">
-        <v>17.28</v>
+        <v>11.96</v>
       </c>
       <c r="F9">
-        <v>79.45999999999999</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="G9">
-        <v>57.94</v>
+        <v>93.48</v>
       </c>
       <c r="H9">
-        <v>77.19</v>
+        <v>44.9</v>
       </c>
       <c r="I9">
-        <v>47.77</v>
+        <v>38.83</v>
       </c>
       <c r="J9">
-        <v>63.43</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1227,28 +1227,28 @@
         <v>29</v>
       </c>
       <c r="C10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="E10">
-        <v>23.14</v>
+        <v>6.56</v>
       </c>
       <c r="F10">
-        <v>57.84</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="G10">
-        <v>91.98999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="H10">
-        <v>80.2</v>
+        <v>42.06</v>
       </c>
       <c r="I10">
-        <v>69.61</v>
+        <v>82.39</v>
       </c>
       <c r="J10">
-        <v>94.17</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1259,28 +1259,28 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="E11">
-        <v>12.53</v>
+        <v>28.32</v>
       </c>
       <c r="F11">
-        <v>28.47</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G11">
-        <v>45.62</v>
+        <v>76.36</v>
       </c>
       <c r="H11">
-        <v>41.58</v>
+        <v>25.82</v>
       </c>
       <c r="I11">
-        <v>75.69</v>
+        <v>84.55</v>
       </c>
       <c r="J11">
-        <v>31.34</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1291,28 +1291,28 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E12">
-        <v>10.14</v>
+        <v>19.86</v>
       </c>
       <c r="F12">
-        <v>32.44</v>
+        <v>35.47</v>
       </c>
       <c r="G12">
-        <v>59.27</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H12">
-        <v>80.09</v>
+        <v>73.11</v>
       </c>
       <c r="I12">
-        <v>89.84</v>
+        <v>36.27</v>
       </c>
       <c r="J12">
-        <v>33.18</v>
+        <v>65.31999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1323,28 +1323,28 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="E13">
-        <v>14.68</v>
+        <v>25.34</v>
       </c>
       <c r="F13">
-        <v>44.28</v>
+        <v>28.87</v>
       </c>
       <c r="G13">
-        <v>68.33</v>
+        <v>35.37</v>
       </c>
       <c r="H13">
-        <v>74.84999999999999</v>
+        <v>89.44</v>
       </c>
       <c r="I13">
-        <v>59.67</v>
+        <v>82.09</v>
       </c>
       <c r="J13">
-        <v>82.89</v>
+        <v>55.99</v>
       </c>
     </row>
   </sheetData>
@@ -1397,28 +1397,28 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="E2">
-        <v>29.97</v>
+        <v>10.82</v>
       </c>
       <c r="F2">
-        <v>35.01</v>
+        <v>71.05</v>
       </c>
       <c r="G2">
-        <v>28.16</v>
+        <v>51.78</v>
       </c>
       <c r="H2">
-        <v>67.38</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="I2">
-        <v>89.88</v>
+        <v>83.83</v>
       </c>
       <c r="J2">
-        <v>83.31</v>
+        <v>27.56</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1429,28 +1429,28 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="E3">
-        <v>12.61</v>
+        <v>25.1</v>
       </c>
       <c r="F3">
-        <v>88.33</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="G3">
-        <v>37.53</v>
+        <v>69.58</v>
       </c>
       <c r="H3">
-        <v>25.41</v>
+        <v>72.5</v>
       </c>
       <c r="I3">
-        <v>93.95</v>
+        <v>58.48</v>
       </c>
       <c r="J3">
-        <v>85.19</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1461,28 +1461,28 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1">
-        <v>46085</v>
+        <v>46081</v>
       </c>
       <c r="E4">
-        <v>2.52</v>
+        <v>10.91</v>
       </c>
       <c r="F4">
-        <v>83.81</v>
+        <v>30.37</v>
       </c>
       <c r="G4">
-        <v>44.07</v>
+        <v>32.25</v>
       </c>
       <c r="H4">
-        <v>30.88</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>48.64</v>
+        <v>64.16</v>
       </c>
       <c r="J4">
-        <v>42.81</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1493,28 +1493,28 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="E5">
-        <v>29.46</v>
+        <v>19.79</v>
       </c>
       <c r="F5">
-        <v>46.63</v>
+        <v>94.52</v>
       </c>
       <c r="G5">
-        <v>62.3</v>
+        <v>54.55</v>
       </c>
       <c r="H5">
-        <v>61.79</v>
+        <v>79.67</v>
       </c>
       <c r="I5">
-        <v>35.08</v>
+        <v>68.81</v>
       </c>
       <c r="J5">
-        <v>25.99</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1525,28 +1525,28 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D6" s="1">
-        <v>46082</v>
+        <v>46084</v>
       </c>
       <c r="E6">
-        <v>29.98</v>
+        <v>5.81</v>
       </c>
       <c r="F6">
-        <v>49.64</v>
+        <v>68.56</v>
       </c>
       <c r="G6">
-        <v>68.81</v>
+        <v>48.55</v>
       </c>
       <c r="H6">
-        <v>93.67</v>
+        <v>88.48</v>
       </c>
       <c r="I6">
-        <v>83.47</v>
+        <v>25.83</v>
       </c>
       <c r="J6">
-        <v>32.31</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1557,28 +1557,28 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="E7">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="F7">
-        <v>60.75</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="G7">
-        <v>78.19</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H7">
-        <v>50.97</v>
+        <v>87.45</v>
       </c>
       <c r="I7">
-        <v>25.07</v>
+        <v>83.56</v>
       </c>
       <c r="J7">
-        <v>25.95</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1589,28 +1589,28 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="E8">
-        <v>28.5</v>
+        <v>22.62</v>
       </c>
       <c r="F8">
-        <v>57.94</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G8">
-        <v>61.44</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="H8">
-        <v>25.1</v>
+        <v>31.08</v>
       </c>
       <c r="I8">
-        <v>45.64</v>
+        <v>56.99</v>
       </c>
       <c r="J8">
-        <v>33.74</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1621,28 +1621,28 @@
         <v>28</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="1">
         <v>46080</v>
       </c>
       <c r="E9">
-        <v>2.92</v>
+        <v>11.35</v>
       </c>
       <c r="F9">
-        <v>68.51000000000001</v>
+        <v>86</v>
       </c>
       <c r="G9">
-        <v>74.43000000000001</v>
+        <v>32.82</v>
       </c>
       <c r="H9">
-        <v>36.57</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="I9">
-        <v>34.12</v>
+        <v>84.86</v>
       </c>
       <c r="J9">
-        <v>51.05</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1653,28 +1653,28 @@
         <v>29</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="E10">
-        <v>3.13</v>
+        <v>20.64</v>
       </c>
       <c r="F10">
-        <v>27.67</v>
+        <v>28.41</v>
       </c>
       <c r="G10">
-        <v>81.56999999999999</v>
+        <v>80.63</v>
       </c>
       <c r="H10">
-        <v>79.11</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="I10">
-        <v>57.95</v>
+        <v>34.61</v>
       </c>
       <c r="J10">
-        <v>71.5</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1685,28 +1685,28 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D11" s="1">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E11">
-        <v>6.09</v>
+        <v>26.41</v>
       </c>
       <c r="F11">
-        <v>27.55</v>
+        <v>59.88</v>
       </c>
       <c r="G11">
-        <v>27.94</v>
+        <v>53.65</v>
       </c>
       <c r="H11">
-        <v>70.25</v>
+        <v>81.22</v>
       </c>
       <c r="I11">
-        <v>79.17</v>
+        <v>45</v>
       </c>
       <c r="J11">
-        <v>45.88</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1717,28 +1717,28 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D12" s="1">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="E12">
-        <v>2.21</v>
+        <v>10.07</v>
       </c>
       <c r="F12">
-        <v>40.38</v>
+        <v>32.92</v>
       </c>
       <c r="G12">
-        <v>32.5</v>
+        <v>25.82</v>
       </c>
       <c r="H12">
-        <v>25.68</v>
+        <v>34.94</v>
       </c>
       <c r="I12">
-        <v>43.84</v>
+        <v>79.27</v>
       </c>
       <c r="J12">
-        <v>59.91</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1749,28 +1749,28 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="E13">
-        <v>9.109999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="F13">
-        <v>33.65</v>
+        <v>72.38</v>
       </c>
       <c r="G13">
-        <v>50.42</v>
+        <v>83.44</v>
       </c>
       <c r="H13">
-        <v>64.7</v>
+        <v>43.78</v>
       </c>
       <c r="I13">
-        <v>54.34</v>
+        <v>72.14</v>
       </c>
       <c r="J13">
-        <v>52.5</v>
+        <v>71.59</v>
       </c>
     </row>
   </sheetData>
@@ -1823,28 +1823,28 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1">
-        <v>46081</v>
+        <v>46086</v>
       </c>
       <c r="E2">
-        <v>4.38</v>
+        <v>21.8</v>
       </c>
       <c r="F2">
-        <v>90.15000000000001</v>
+        <v>55.18</v>
       </c>
       <c r="G2">
-        <v>82.59</v>
+        <v>35.11</v>
       </c>
       <c r="H2">
-        <v>87.84</v>
+        <v>91.31</v>
       </c>
       <c r="I2">
-        <v>53.15</v>
+        <v>94.13</v>
       </c>
       <c r="J2">
-        <v>69.14</v>
+        <v>91.27</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1855,28 +1855,28 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="E3">
-        <v>21.7</v>
+        <v>28.51</v>
       </c>
       <c r="F3">
-        <v>92.69</v>
+        <v>48.81</v>
       </c>
       <c r="G3">
-        <v>67.95</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H3">
-        <v>72.03</v>
+        <v>50.25</v>
       </c>
       <c r="I3">
-        <v>77.28</v>
+        <v>62.23</v>
       </c>
       <c r="J3">
-        <v>30.18</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1887,28 +1887,28 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E4">
-        <v>11.06</v>
+        <v>23.51</v>
       </c>
       <c r="F4">
-        <v>68.79000000000001</v>
+        <v>39.7</v>
       </c>
       <c r="G4">
-        <v>32.45</v>
+        <v>75.25</v>
       </c>
       <c r="H4">
-        <v>62.67</v>
+        <v>94.8</v>
       </c>
       <c r="I4">
-        <v>72.52</v>
+        <v>34.14</v>
       </c>
       <c r="J4">
-        <v>43.34</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1919,28 +1919,28 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1">
         <v>46083</v>
       </c>
       <c r="E5">
-        <v>25.59</v>
+        <v>7.17</v>
       </c>
       <c r="F5">
-        <v>60.31</v>
+        <v>66.73</v>
       </c>
       <c r="G5">
-        <v>88.04000000000001</v>
+        <v>28.99</v>
       </c>
       <c r="H5">
-        <v>88.27</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="I5">
-        <v>82.05</v>
+        <v>26.52</v>
       </c>
       <c r="J5">
-        <v>56.05</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1954,25 +1954,25 @@
         <v>54</v>
       </c>
       <c r="D6" s="1">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="E6">
-        <v>11.27</v>
+        <v>2.6</v>
       </c>
       <c r="F6">
-        <v>66.84999999999999</v>
+        <v>45.51</v>
       </c>
       <c r="G6">
-        <v>74.76000000000001</v>
+        <v>59.82</v>
       </c>
       <c r="H6">
-        <v>43.43</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I6">
-        <v>51.51</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="J6">
-        <v>92.34999999999999</v>
+        <v>67.92</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1983,28 +1983,28 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="E7">
-        <v>6.41</v>
+        <v>24.38</v>
       </c>
       <c r="F7">
-        <v>67.89</v>
+        <v>69.27</v>
       </c>
       <c r="G7">
-        <v>45.69</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H7">
-        <v>50.4</v>
+        <v>67.59</v>
       </c>
       <c r="I7">
-        <v>54.63</v>
+        <v>50.7</v>
       </c>
       <c r="J7">
-        <v>66.39</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2015,28 +2015,28 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="D8" s="1">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="E8">
-        <v>8.9</v>
+        <v>14.85</v>
       </c>
       <c r="F8">
-        <v>30.29</v>
+        <v>30.73</v>
       </c>
       <c r="G8">
-        <v>50.98</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="H8">
-        <v>29.52</v>
+        <v>54.62</v>
       </c>
       <c r="I8">
-        <v>70.44</v>
+        <v>39.66</v>
       </c>
       <c r="J8">
-        <v>36.62</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2047,28 +2047,28 @@
         <v>28</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="E9">
-        <v>29.96</v>
+        <v>27.16</v>
       </c>
       <c r="F9">
-        <v>54.45</v>
+        <v>69.77</v>
       </c>
       <c r="G9">
-        <v>72.31999999999999</v>
+        <v>57.34</v>
       </c>
       <c r="H9">
-        <v>51.73</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="I9">
-        <v>75.08</v>
+        <v>39.11</v>
       </c>
       <c r="J9">
-        <v>33.43</v>
+        <v>69.27</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2079,28 +2079,28 @@
         <v>29</v>
       </c>
       <c r="C10">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="E10">
-        <v>9.609999999999999</v>
+        <v>25.45</v>
       </c>
       <c r="F10">
-        <v>56.52</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="G10">
-        <v>52.26</v>
+        <v>63.78</v>
       </c>
       <c r="H10">
-        <v>88.29000000000001</v>
+        <v>30.53</v>
       </c>
       <c r="I10">
-        <v>41.04</v>
+        <v>32.77</v>
       </c>
       <c r="J10">
-        <v>32.39</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2111,28 +2111,28 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1">
-        <v>46081</v>
+        <v>46085</v>
       </c>
       <c r="E11">
-        <v>8.26</v>
+        <v>2.11</v>
       </c>
       <c r="F11">
-        <v>87.66</v>
+        <v>26.97</v>
       </c>
       <c r="G11">
-        <v>62.59</v>
+        <v>62.32</v>
       </c>
       <c r="H11">
-        <v>75.79000000000001</v>
+        <v>35.46</v>
       </c>
       <c r="I11">
-        <v>51.1</v>
+        <v>41.6</v>
       </c>
       <c r="J11">
-        <v>25.41</v>
+        <v>58.98</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2143,28 +2143,28 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="E12">
-        <v>17.42</v>
+        <v>15.57</v>
       </c>
       <c r="F12">
-        <v>81.06</v>
+        <v>76.23</v>
       </c>
       <c r="G12">
-        <v>76.53</v>
+        <v>91.91</v>
       </c>
       <c r="H12">
-        <v>59.94</v>
+        <v>51.57</v>
       </c>
       <c r="I12">
-        <v>31.84</v>
+        <v>29.84</v>
       </c>
       <c r="J12">
-        <v>39.95</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2175,28 +2175,28 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1">
-        <v>46081</v>
+        <v>46085</v>
       </c>
       <c r="E13">
-        <v>22.18</v>
+        <v>12.35</v>
       </c>
       <c r="F13">
-        <v>32.71</v>
+        <v>34.51</v>
       </c>
       <c r="G13">
-        <v>62.33</v>
+        <v>58.95</v>
       </c>
       <c r="H13">
-        <v>53.21</v>
+        <v>72.3</v>
       </c>
       <c r="I13">
-        <v>69.14</v>
+        <v>93.88</v>
       </c>
       <c r="J13">
-        <v>79.40000000000001</v>
+        <v>76.92</v>
       </c>
     </row>
   </sheetData>
